--- a/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
@@ -1002,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>1260.4639571819057</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>5739.5360428180938</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>57121.599273614636</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>42878.400726385364</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1036,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>1145.3772939121209</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>5854.6227060878791</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>51266.976567526755</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>48733.023432473245</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1130,7 +1134,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>70000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>62861.13531643273</v>
+        <v>51266.976567526755</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1235,7 +1239,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>37138.86468356727</v>
+        <v>48733.023432473245</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
@@ -1074,31 +1074,33 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>1027.9829632692656</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>5972.0170367307346</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>45294.959530796019</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>54705.040469203981</v>
       </c>
       <c r="J11" s="14"/>
     </row>
@@ -1134,7 +1136,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1169,7 +1171,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>56000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1204,7 +1206,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>51266.976567526755</v>
+        <v>45294.959530796019</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1239,7 +1241,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>48733.023432473245</v>
+        <v>54705.040469203981</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Khurai_Ahongei _Group_Weekly.xlsx
@@ -1105,73 +1105,77 @@
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
+      <c r="A12" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>908.23469291775018</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
+        <v>6091.7653070822498</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>39203.19422371377</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>60796.80577628623</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
+      <c r="A13" s="19">
+        <v>46307</v>
+      </c>
+      <c r="B13" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>786.08528268937505</v>
+      </c>
+      <c r="F13" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
+        <v>6213.9147173106248</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>32989.279506403145</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>67010.720493596862</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>49000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1206,7 +1210,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>45294.959530796019</v>
+        <v>32989.279506403145</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1241,7 +1245,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>54705.040469203981</v>
+        <v>67010.720493596862</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
